--- a/data/trending_integrated_20260916_10.xlsx
+++ b/data/trending_integrated_20260916_10.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F2" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G2" t="n">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>6951001410</v>
+        <v>6982497090</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3905</v>
+        <v>4595</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.10%</t>
+          <t>'+11.53%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>235</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
-        <v>3.11</v>
+        <v>0.74</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3515</v>
+        <v>4120</v>
       </c>
       <c r="K3" t="n">
         <v>4120</v>
       </c>
       <c r="L3" t="n">
-        <v>4140</v>
+        <v>4800</v>
       </c>
       <c r="M3" t="n">
-        <v>3840</v>
+        <v>4100</v>
       </c>
       <c r="N3" t="n">
-        <v>3.16</v>
+        <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>9315004717</v>
+        <v>188813376043</v>
       </c>
       <c r="P3" t="n">
-        <v>16110</v>
+        <v>8100</v>
       </c>
       <c r="Q3" t="n">
-        <v>2300</v>
+        <v>592</v>
       </c>
       <c r="R3" t="n">
-        <v>-383000</v>
+        <v>188000</v>
       </c>
       <c r="S3" t="n">
-        <v>-140000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-2026년 대규모 적자 및 상폐 가능성 우려. 공매도 및 주가 조작 의혹 제기.</t>
+          <t>AI 데이터센터 투자 수혜 기대감 언급. 외국인 동시호가 매수 및 돌파 기대감 표출.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '공매도']</t>
+          <t>['AI', '데이터센터', '수혜']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4405</v>
+        <v>3840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.92%</t>
+          <t>'+9.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>115</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
-        <v>0.74</v>
+        <v>3.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4120</v>
+        <v>3515</v>
       </c>
       <c r="K4" t="n">
         <v>4120</v>
       </c>
       <c r="L4" t="n">
-        <v>4800</v>
+        <v>4140</v>
       </c>
       <c r="M4" t="n">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>3.16</v>
       </c>
       <c r="O4" t="n">
-        <v>172192498591</v>
+        <v>9990233174</v>
       </c>
       <c r="P4" t="n">
-        <v>8100</v>
+        <v>16110</v>
       </c>
       <c r="Q4" t="n">
-        <v>592</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>188000</v>
+        <v>-383000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-140000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>광통신 섹터의 상승 흐름 속 주가 상승 기대감 표출. AI 데이터센터 투자 수혜 가능성 언급.</t>
+          <t>2025-2026년 대규모 적자 및 상폐 가능성 우려. 공매도 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', 'AI 데이터센터', '주가 상승']</t>
+          <t>['적자', '상폐', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14790</v>
+        <v>15010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.60%</t>
+          <t>'+6.15%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="H5" t="n">
         <v>1.95</v>
@@ -886,7 +886,7 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>147854755810</v>
+        <v>163479153855</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 테마 상승 및 경쟁 종목 강세 언급. 단기 주가 상승 기대감 표출.</t>
+          <t>광통신 섹터 강세에 따른 주가 상승 기대감. 14000원 지지선 확보 및 120일선 저항대 돌파 여부 관망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '통신장비', '주가 상승']</t>
+          <t>['광통신', '섹터', '지지선']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18300</v>
+        <v>5420</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+3.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>-1.39</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45</v>
+        <v>1.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17550</v>
+        <v>5230</v>
       </c>
       <c r="K6" t="n">
-        <v>17150</v>
+        <v>5750</v>
       </c>
       <c r="L6" t="n">
-        <v>18860</v>
+        <v>5880</v>
       </c>
       <c r="M6" t="n">
-        <v>17020</v>
+        <v>5200</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>102406532630</v>
+        <v>45181720035</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>8980</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>2795</v>
       </c>
       <c r="R6" t="n">
-        <v>65000</v>
+        <v>259000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 보안주 및 양자보안 테마 상승 언급. 개미 털기 의혹 및 인수합병 기대감 표출.</t>
+          <t>트럼프 양자암호 행정명령 및 미 보안주 상승에 따른 기대감. 삼성과의 계약 및 스테이블코인 법안 부결 이슈 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '인수합병']</t>
+          <t>['양자암호', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5450</v>
+        <v>1716000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.21%</t>
+          <t>'+1.54%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.39</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>783</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>463</v>
       </c>
       <c r="G7" t="n">
-        <v>136</v>
+        <v>2337</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29</v>
+        <v>50.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5230</v>
+        <v>1690000</v>
       </c>
       <c r="K7" t="n">
-        <v>5750</v>
+        <v>1686000</v>
       </c>
       <c r="L7" t="n">
-        <v>5880</v>
+        <v>1731000</v>
       </c>
       <c r="M7" t="n">
-        <v>5200</v>
+        <v>1686000</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>50.27</v>
       </c>
       <c r="O7" t="n">
-        <v>43366440365</v>
+        <v>1243376501000</v>
       </c>
       <c r="P7" t="n">
-        <v>8980</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>2795</v>
+        <v>331500</v>
       </c>
       <c r="R7" t="n">
-        <v>259000</v>
+        <v>18000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>트럼프 양자암호 행정명령 및 미국 보안주 상승 언급. 스테이블코인 법안 부결로 인한 하락 가능성 제기.</t>
+          <t>미국 반도체 선물 급등 및 인텔 사장 발언 인용. 단기 조정 후 상승 전망 및 자사주 매입 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자암호', '보안주', '스테이블코인']</t>
+          <t>['반도체', '선물', '자사주 매입']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3460</v>
+        <v>3410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.98%</t>
+          <t>'+1.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>73842490167</v>
+        <v>76156266425</v>
       </c>
       <c r="P8" t="n">
         <v>5100</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양자암호 테마 관련 트럼프 행정명령 및 미국 보안주 상승 언급. 매집 흔적 및 롤링 구간에 대한 주의.</t>
+          <t>양자암호 행정명령 관련 기대감 속 주가 상승 및 하락 반복. 매집 신호 및 저항대 돌파 여부 관망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자암호', '보안주', '매집']</t>
+          <t>['양자암호', '행정명령', '매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1721000</v>
+        <v>250500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.83%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="F9" t="n">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="G9" t="n">
-        <v>2278</v>
+        <v>2395</v>
       </c>
       <c r="H9" t="n">
-        <v>50.2</v>
+        <v>46.56</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1690000</v>
+        <v>248500</v>
       </c>
       <c r="K9" t="n">
-        <v>1686000</v>
+        <v>248000</v>
       </c>
       <c r="L9" t="n">
-        <v>1731000</v>
+        <v>251500</v>
       </c>
       <c r="M9" t="n">
-        <v>1686000</v>
+        <v>247500</v>
       </c>
       <c r="N9" t="n">
-        <v>50.27</v>
+        <v>46.57</v>
       </c>
       <c r="O9" t="n">
-        <v>1131565046500</v>
+        <v>656404013000</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>331500</v>
+        <v>76700</v>
       </c>
       <c r="R9" t="n">
-        <v>18000</v>
+        <v>-496000</v>
       </c>
       <c r="S9" t="n">
-        <v>26000</v>
+        <v>23000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 반도체 선물 급등 및 인텔 사장 발언 인용. 단기 조정 후 상승 전망 및 자사주 매입 기대감.</t>
+          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '자사주 매입']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250750</v>
+        <v>17560</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.91%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>732</v>
+        <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>421</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>2346</v>
+        <v>158</v>
       </c>
       <c r="H10" t="n">
-        <v>46.56</v>
+        <v>0.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>248500</v>
+        <v>17550</v>
       </c>
       <c r="K10" t="n">
-        <v>248000</v>
+        <v>17150</v>
       </c>
       <c r="L10" t="n">
-        <v>251500</v>
+        <v>18860</v>
       </c>
       <c r="M10" t="n">
-        <v>247500</v>
+        <v>17020</v>
       </c>
       <c r="N10" t="n">
-        <v>46.57</v>
+        <v>0.35</v>
       </c>
       <c r="O10" t="n">
-        <v>612782554250</v>
+        <v>124813736770</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>30550</v>
       </c>
       <c r="Q10" t="n">
-        <v>76700</v>
+        <v>6100</v>
       </c>
       <c r="R10" t="n">
-        <v>-496000</v>
+        <v>65000</v>
       </c>
       <c r="S10" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
+          <t>미국 보안주 상승 및 양자암호 관련 기대감 속 주가 변동성. 개미 털기 의혹 및 물량 흡수 중 관측.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['보안주', '양자암호', '변동성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8490</v>
+        <v>10600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.5</v>
+        <v>1.29</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
         <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="H11" t="n">
-        <v>26.66</v>
+        <v>19.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8610</v>
+        <v>10660</v>
       </c>
       <c r="K11" t="n">
-        <v>8600</v>
+        <v>10500</v>
       </c>
       <c r="L11" t="n">
-        <v>8610</v>
+        <v>10900</v>
       </c>
       <c r="M11" t="n">
-        <v>8460</v>
+        <v>10060</v>
       </c>
       <c r="N11" t="n">
-        <v>27.16</v>
+        <v>17.93</v>
       </c>
       <c r="O11" t="n">
-        <v>4803170440</v>
+        <v>69123097055</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>8120</v>
+        <v>1760</v>
       </c>
       <c r="R11" t="n">
-        <v>-292000</v>
+        <v>-437000</v>
       </c>
       <c r="S11" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 부진 및 환율 영향 언급. 외인 매도세와 낮은 PBR 지적, 일부 긍정적 기술 기대.</t>
+          <t>특정 가격대 거래량 발생 시 20% 상승 기대. 현재 주가 조작 의혹 및 종목 교체 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['3분기 실적', '환율', '외인 매도']</t>
+          <t>['거래량', '상승', '조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84800</v>
+        <v>14710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.62%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>452</v>
+        <v>379</v>
       </c>
       <c r="H12" t="n">
-        <v>23.37</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>86200</v>
+        <v>14980</v>
       </c>
       <c r="K12" t="n">
-        <v>86200</v>
+        <v>15300</v>
       </c>
       <c r="L12" t="n">
-        <v>86300</v>
+        <v>15580</v>
       </c>
       <c r="M12" t="n">
-        <v>84400</v>
+        <v>14600</v>
       </c>
       <c r="N12" t="n">
-        <v>23.45</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>45034682900</v>
+        <v>18453304775</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>-105000</v>
+        <v>-19000</v>
       </c>
       <c r="S12" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 언급 및 공매도 세력에 대한 비판. 단기 상승 기대.</t>
+          <t>국제유가 상승 및 지정학적 이슈로 인한 기대감 속 변동성. 비축유 물량 및 역배열 하락세 관측.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
+          <t>['국제유가', '지정학', '변동성']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14720</v>
+        <v>84600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>370</v>
+        <v>457</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>23.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>86200</v>
       </c>
       <c r="K13" t="n">
-        <v>15300</v>
+        <v>86200</v>
       </c>
       <c r="L13" t="n">
-        <v>15580</v>
+        <v>86300</v>
       </c>
       <c r="M13" t="n">
-        <v>14600</v>
+        <v>84400</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>23.45</v>
       </c>
       <c r="O13" t="n">
-        <v>17942833090</v>
+        <v>48851364900</v>
       </c>
       <c r="P13" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-19000</v>
+        <v>-105000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 에너지주 폭등 가능성 언급, 파병 이슈 기대. 그러나 비축유 및 유가 하락 추세 우려도 존재.</t>
+          <t>웨스팅하우스 지분 인수 관련 언급 및 공매도 세력에 대한 비판. 단기 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국제유가', '에너지주', '파병이슈']</t>
+          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18710</v>
+        <v>8440</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.20%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.11</v>
+        <v>-0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H14" t="n">
-        <v>10.64</v>
+        <v>26.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19130</v>
+        <v>8610</v>
       </c>
       <c r="K14" t="n">
-        <v>19160</v>
+        <v>8600</v>
       </c>
       <c r="L14" t="n">
-        <v>19340</v>
+        <v>8610</v>
       </c>
       <c r="M14" t="n">
-        <v>18610</v>
+        <v>8440</v>
       </c>
       <c r="N14" t="n">
-        <v>10.53</v>
+        <v>27.16</v>
       </c>
       <c r="O14" t="n">
-        <v>21772375280</v>
+        <v>6267325100</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>8120</v>
       </c>
       <c r="R14" t="n">
-        <v>-112000</v>
+        <v>-292000</v>
       </c>
       <c r="S14" t="n">
-        <v>-2000</v>
+        <v>-4000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차 해지 운동 동참 독려와 함께 단기 주가 상승 기대감 표출. 명분 없는 파병 비판.</t>
+          <t>수익성 부진 및 높은 부채 비율에 대한 우려 제기. 외인 매도세 관측 및 배당 기대감 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차 해지', '주가 상승', '파병']</t>
+          <t>['부채', '외인매도', '배당']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10370</v>
+        <v>18540</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.72%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.29</v>
+        <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>213</v>
       </c>
       <c r="H15" t="n">
-        <v>19.22</v>
+        <v>10.64</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10660</v>
+        <v>19130</v>
       </c>
       <c r="K15" t="n">
-        <v>10500</v>
+        <v>19160</v>
       </c>
       <c r="L15" t="n">
-        <v>10900</v>
+        <v>19340</v>
       </c>
       <c r="M15" t="n">
-        <v>10060</v>
+        <v>18500</v>
       </c>
       <c r="N15" t="n">
-        <v>17.93</v>
+        <v>10.53</v>
       </c>
       <c r="O15" t="n">
-        <v>64657389580</v>
+        <v>24018074080</v>
       </c>
       <c r="P15" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>1760</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-437000</v>
+        <v>-112000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>광통신 테마 내에서 주가 하락 및 변동성에 대한 언급. 특정 가격대 거래량 발생 시 상승 가능성 언급.</t>
+          <t>대차해지운동 참여 독려와 함께 주가 상승 기대감 표출. 호르무즈 파병 및 대미 투자 발표 등 거시 경제 이슈 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '거래량', '변동성']</t>
+          <t>['대차해지', '상승', '파병']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31300</v>
+        <v>30950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-4.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.34</v>
       </c>
       <c r="E16" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="H16" t="n">
         <v>17.16</v>
@@ -1892,13 +1892,13 @@
         <v>32850</v>
       </c>
       <c r="M16" t="n">
-        <v>31200</v>
+        <v>30900</v>
       </c>
       <c r="N16" t="n">
         <v>17.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4134742400</v>
+        <v>4827143500</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>과거 간암 신약 실패 경험 기반 하방 베팅 유지. 유럽 담관암 신약 신청이 FDA 실패 가능성 및 개미 압살 전략이라는 분석.</t>
+          <t>HLB 주가 하락 베팅 유지 및 유럽 담관암 신약 신청 관련 불확실성 제기. FDA 승인 실패 시 주가 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['간암신약', '담관암', 'EMA신청']</t>
+          <t>['간암', '담관암', 'FDA']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5870</v>
+        <v>5880</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.97%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.04</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
         <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="H17" t="n">
         <v>0.98</v>
@@ -1990,7 +1990,7 @@
         <v>3.02</v>
       </c>
       <c r="O17" t="n">
-        <v>33695462720</v>
+        <v>35125444020</v>
       </c>
       <c r="P17" t="n">
         <v>11370</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미 클래리티법 부결 및 이스타항공 공급 계약 소식에도 불구하고, 삼성과의 공급 계약 규모 및 가상자산 시장 약세 영향.</t>
+          <t>가상자산 규제 법안 부결 및 공매도 증가로 인한 주가 하락. 양자내성암호 OTP 공급 등 호재 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자내성암호', '공급계약', '가상자산']</t>
+          <t>['가상자산', '공매도', '양자암호']</t>
         </is>
       </c>
       <c r="X17" t="n">

--- a/data/trending_integrated_20260916_10.xlsx
+++ b/data/trending_integrated_20260916_10.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>6982497090</v>
+        <v>7042093890</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4595</v>
+        <v>4590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.53%</t>
+          <t>'+11.41%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H3" t="n">
         <v>0.74</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>188813376043</v>
+        <v>205693668481</v>
       </c>
       <c r="P3" t="n">
         <v>8100</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 데이터센터 투자 수혜 기대감 언급. 외국인 동시호가 매수 및 돌파 기대감 표출.</t>
+          <t>AI 데이터센터 투자 수혜 기대. 외국인 매수 동시호가 폭등 가능성 언급. 하반기 2등 자리 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI', '데이터센터', '수혜']</t>
+          <t>['AI', '데이터센터', '외국인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3840</v>
+        <v>3820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.25%</t>
+          <t>'+8.68%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H4" t="n">
         <v>3.11</v>
@@ -794,7 +794,7 @@
         <v>3.16</v>
       </c>
       <c r="O4" t="n">
-        <v>9990233174</v>
+        <v>10410967332</v>
       </c>
       <c r="P4" t="n">
         <v>16110</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15010</v>
+        <v>15290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.15%</t>
+          <t>'+8.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="H5" t="n">
         <v>1.95</v>
@@ -877,7 +877,7 @@
         <v>14420</v>
       </c>
       <c r="L5" t="n">
-        <v>15250</v>
+        <v>15400</v>
       </c>
       <c r="M5" t="n">
         <v>14300</v>
@@ -886,7 +886,7 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>163479153855</v>
+        <v>201641769925</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세에 따른 주가 상승 기대감. 14000원 지지선 확보 및 120일선 저항대 돌파 여부 관망.</t>
+          <t>미국 증시 통신장비 및 부품주 강세. 14000원 지지선 확보 및 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '섹터', '지지선']</t>
+          <t>['통신장비', '부품', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5420</v>
+        <v>5410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.63%</t>
+          <t>'+3.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.39</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H6" t="n">
         <v>1.29</v>
@@ -978,7 +978,7 @@
         <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>45181720035</v>
+        <v>46095909470</v>
       </c>
       <c r="P6" t="n">
         <v>8980</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>트럼프 양자암호 행정명령 및 미 보안주 상승에 따른 기대감. 삼성과의 계약 및 스테이블코인 법안 부결 이슈 언급.</t>
+          <t>트럼프 양자암호 PQC 행정명령 및 미국 사이버보안주 폭등 수혜 기대. 삼성과 대규모 계약 체결.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자암호', '보안주', '계약']</t>
+          <t>['양자암호', '사이버보안', '계약']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1716000</v>
+        <v>3435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.54%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="E7" t="n">
-        <v>783</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>463</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>2337</v>
+        <v>141</v>
       </c>
       <c r="H7" t="n">
-        <v>50.2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1690000</v>
+        <v>3360</v>
       </c>
       <c r="K7" t="n">
-        <v>1686000</v>
+        <v>3570</v>
       </c>
       <c r="L7" t="n">
-        <v>1731000</v>
+        <v>3910</v>
       </c>
       <c r="M7" t="n">
-        <v>1686000</v>
+        <v>3345</v>
       </c>
       <c r="N7" t="n">
-        <v>50.27</v>
+        <v>1.34</v>
       </c>
       <c r="O7" t="n">
-        <v>1243376501000</v>
+        <v>77509509801</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>5100</v>
       </c>
       <c r="Q7" t="n">
-        <v>331500</v>
+        <v>966</v>
       </c>
       <c r="R7" t="n">
-        <v>18000</v>
+        <v>113000</v>
       </c>
       <c r="S7" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 반도체 선물 급등 및 인텔 사장 발언 인용. 단기 조정 후 상승 전망 및 자사주 매입 기대감.</t>
+          <t>양자내성암호 행정명령 수혜 기대. 글로벌 기업 양자암호 해독키 독점 공급 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '자사주 매입']</t>
+          <t>['양자암호', '보안', '공급']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3410</v>
+        <v>1713000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.49%</t>
+          <t>'+1.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.34</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>477</v>
       </c>
       <c r="G8" t="n">
-        <v>130</v>
+        <v>2329</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3360</v>
+        <v>1690000</v>
       </c>
       <c r="K8" t="n">
-        <v>3570</v>
+        <v>1686000</v>
       </c>
       <c r="L8" t="n">
-        <v>3910</v>
+        <v>1731000</v>
       </c>
       <c r="M8" t="n">
-        <v>3345</v>
+        <v>1686000</v>
       </c>
       <c r="N8" t="n">
-        <v>1.34</v>
+        <v>50.27</v>
       </c>
       <c r="O8" t="n">
-        <v>76156266425</v>
+        <v>1325856738500</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>966</v>
+        <v>331500</v>
       </c>
       <c r="R8" t="n">
-        <v>113000</v>
+        <v>18000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양자암호 행정명령 관련 기대감 속 주가 상승 및 하락 반복. 매집 신호 및 저항대 돌파 여부 관망.</t>
+          <t>미국 증시 반도체 선물 급등 및 인텔 사장 발언 인용. 조정 끝났다는 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자암호', '행정명령', '매집']</t>
+          <t>['반도체', '선물', '급등']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250500</v>
+        <v>249500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="F9" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="G9" t="n">
-        <v>2395</v>
+        <v>2357</v>
       </c>
       <c r="H9" t="n">
         <v>46.56</v>
@@ -1254,7 +1254,7 @@
         <v>46.57</v>
       </c>
       <c r="O9" t="n">
-        <v>656404013000</v>
+        <v>715501949500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
+          <t>금리 인상 및 정치적 이슈 언급. 반도체 업황 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['금리', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17560</v>
+        <v>10670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>1.29</v>
       </c>
       <c r="E10" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="H10" t="n">
-        <v>0.45</v>
+        <v>19.22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17550</v>
+        <v>10660</v>
       </c>
       <c r="K10" t="n">
-        <v>17150</v>
+        <v>10500</v>
       </c>
       <c r="L10" t="n">
-        <v>18860</v>
+        <v>10900</v>
       </c>
       <c r="M10" t="n">
-        <v>17020</v>
+        <v>10060</v>
       </c>
       <c r="N10" t="n">
-        <v>0.35</v>
+        <v>17.93</v>
       </c>
       <c r="O10" t="n">
-        <v>124813736770</v>
+        <v>75885279320</v>
       </c>
       <c r="P10" t="n">
-        <v>30550</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>6100</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>65000</v>
+        <v>-437000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 보안주 상승 및 양자암호 관련 기대감 속 주가 변동성. 개미 털기 의혹 및 물량 흡수 중 관측.</t>
+          <t>거래량 증가 시 20% 상승 기대. 광통신 관련주로 분류되나 주의 종목 지정.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', '양자암호', '변동성']</t>
+          <t>['거래량', '상승', '주의']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10600</v>
+        <v>17300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-1.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.29</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="H11" t="n">
-        <v>19.22</v>
+        <v>0.45</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10660</v>
+        <v>17550</v>
       </c>
       <c r="K11" t="n">
-        <v>10500</v>
+        <v>17150</v>
       </c>
       <c r="L11" t="n">
-        <v>10900</v>
+        <v>18860</v>
       </c>
       <c r="M11" t="n">
-        <v>10060</v>
+        <v>17020</v>
       </c>
       <c r="N11" t="n">
-        <v>17.93</v>
+        <v>0.35</v>
       </c>
       <c r="O11" t="n">
-        <v>69123097055</v>
+        <v>133340128315</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>30550</v>
       </c>
       <c r="Q11" t="n">
-        <v>1760</v>
+        <v>6100</v>
       </c>
       <c r="R11" t="n">
-        <v>-437000</v>
+        <v>65000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>특정 가격대 거래량 발생 시 20% 상승 기대. 현재 주가 조작 의혹 및 종목 교체 가능성 언급.</t>
+          <t>미국 보안주 상승 마감. 상용화 및 매출 발생 기업. 개미 털기 위한 인위적 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '상승', '조작']</t>
+          <t>['보안', '상용화', '매출']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14710</v>
+        <v>8440</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>379</v>
+        <v>219</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14980</v>
+        <v>8610</v>
       </c>
       <c r="K12" t="n">
-        <v>15300</v>
+        <v>8600</v>
       </c>
       <c r="L12" t="n">
-        <v>15580</v>
+        <v>8610</v>
       </c>
       <c r="M12" t="n">
-        <v>14600</v>
+        <v>8430</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O12" t="n">
-        <v>18453304775</v>
+        <v>6998518550</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>8120</v>
       </c>
       <c r="R12" t="n">
-        <v>-19000</v>
+        <v>-292000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 지정학적 이슈로 인한 기대감 속 변동성. 비축유 물량 및 역배열 하락세 관측.</t>
+          <t>빚 과다 및 실적 부진 언급. 외인 매도세 포착. 3분기 일시적 하락 원인 분석.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학', '변동성']</t>
+          <t>['빚', '실적', '외인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84600</v>
+        <v>14660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="H13" t="n">
-        <v>23.37</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>86200</v>
+        <v>14980</v>
       </c>
       <c r="K13" t="n">
-        <v>86200</v>
+        <v>15300</v>
       </c>
       <c r="L13" t="n">
-        <v>86300</v>
+        <v>15580</v>
       </c>
       <c r="M13" t="n">
-        <v>84400</v>
+        <v>14600</v>
       </c>
       <c r="N13" t="n">
-        <v>23.45</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>48851364900</v>
+        <v>19022109685</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R13" t="n">
-        <v>-105000</v>
+        <v>-19000</v>
       </c>
       <c r="S13" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 언급 및 공매도 세력에 대한 비판. 단기 상승 기대.</t>
+          <t>국제 유가 상승 기대감과 에너지주 폭등 가능성 언급. 다만, 비축유 및 유가 하락 추세에 대한 우려와 테마 소멸 가능성 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
+          <t>['국제유가', '에너지주', '테마']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8440</v>
+        <v>84300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-2.20%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.5</v>
+        <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="G14" t="n">
-        <v>202</v>
+        <v>479</v>
       </c>
       <c r="H14" t="n">
-        <v>26.66</v>
+        <v>23.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8610</v>
+        <v>86200</v>
       </c>
       <c r="K14" t="n">
-        <v>8600</v>
+        <v>86200</v>
       </c>
       <c r="L14" t="n">
-        <v>8610</v>
+        <v>86300</v>
       </c>
       <c r="M14" t="n">
-        <v>8440</v>
+        <v>84200</v>
       </c>
       <c r="N14" t="n">
-        <v>27.16</v>
+        <v>23.45</v>
       </c>
       <c r="O14" t="n">
-        <v>6267325100</v>
+        <v>54354833250</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-292000</v>
+        <v>-105000</v>
       </c>
       <c r="S14" t="n">
-        <v>-4000</v>
+        <v>-21000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>수익성 부진 및 높은 부채 비율에 대한 우려 제기. 외인 매도세 관측 및 배당 기대감 언급.</t>
+          <t>웨스팅하우스 지분 인수 관련 언급 및 공매도 세력에 대한 비판. 단기 상승 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['부채', '외인매도', '배당']</t>
+          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18540</v>
+        <v>18530</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-3.14%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H15" t="n">
         <v>10.64</v>
@@ -1806,7 +1806,7 @@
         <v>10.53</v>
       </c>
       <c r="O15" t="n">
-        <v>24018074080</v>
+        <v>25443876110</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차해지운동 참여 독려와 함께 주가 상승 기대감 표출. 호르무즈 파병 및 대미 투자 발표 등 거시 경제 이슈 언급.</t>
+          <t>대차해지 운동 독려. 2~3일 만원 이상 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차해지', '상승', '파병']</t>
+          <t>['대차해지', '상승', '운동']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30950</v>
+        <v>31100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.34</v>
       </c>
       <c r="E16" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G16" t="n">
-        <v>728</v>
+        <v>786</v>
       </c>
       <c r="H16" t="n">
         <v>17.16</v>
@@ -1898,7 +1898,7 @@
         <v>17.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4827143500</v>
+        <v>5357146650</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5880</v>
+        <v>5890</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-6.66%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.04</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H17" t="n">
         <v>0.98</v>
@@ -1990,7 +1990,7 @@
         <v>3.02</v>
       </c>
       <c r="O17" t="n">
-        <v>35125444020</v>
+        <v>35865070275</v>
       </c>
       <c r="P17" t="n">
         <v>11370</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>가상자산 규제 법안 부결 및 공매도 증가로 인한 주가 하락. 양자내성암호 OTP 공급 등 호재 언급.</t>
+          <t>클래리티법 부결 소식과 양자내성암호 OTP 공급 계약 뉴스에 대한 엇갈린 반응. 외국인 매수세와 공매도 현황, 보안주 테마 상승세에 대한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['가상자산', '공매도', '양자암호']</t>
+          <t>['양자내성암호', 'OTP', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">

--- a/data/trending_integrated_20260916_10.xlsx
+++ b/data/trending_integrated_20260916_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7042093890</v>
+        <v>7063044930</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4590</v>
+        <v>13850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.41%</t>
+          <t>'+29.44%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4120</v>
+        <v>10700</v>
       </c>
       <c r="K3" t="n">
-        <v>4120</v>
+        <v>10800</v>
       </c>
       <c r="L3" t="n">
-        <v>4800</v>
+        <v>13900</v>
       </c>
       <c r="M3" t="n">
-        <v>4100</v>
+        <v>10740</v>
       </c>
       <c r="N3" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>205693668481</v>
+        <v>135962495305</v>
       </c>
       <c r="P3" t="n">
-        <v>8100</v>
+        <v>25700</v>
       </c>
       <c r="Q3" t="n">
-        <v>592</v>
+        <v>4600</v>
       </c>
       <c r="R3" t="n">
-        <v>188000</v>
+        <v>12000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 데이터센터 투자 수혜 기대. 외국인 매수 동시호가 폭등 가능성 언급. 하반기 2등 자리 전망.</t>
+          <t>광통신, 6G, 5G 대장주로서의 기대감과 함께 빛과전자와의 동반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI', '데이터센터', '외국인']</t>
+          <t>['광통신', '6G', '5G']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3820</v>
+        <v>4680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.68%</t>
+          <t>'+13.59%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>245</v>
+        <v>118</v>
       </c>
       <c r="H4" t="n">
-        <v>3.11</v>
+        <v>0.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3515</v>
+        <v>4120</v>
       </c>
       <c r="K4" t="n">
         <v>4120</v>
       </c>
       <c r="L4" t="n">
-        <v>4140</v>
+        <v>4800</v>
       </c>
       <c r="M4" t="n">
-        <v>3800</v>
+        <v>4100</v>
       </c>
       <c r="N4" t="n">
-        <v>3.16</v>
+        <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>10410967332</v>
+        <v>229728012497</v>
       </c>
       <c r="P4" t="n">
-        <v>16110</v>
+        <v>8100</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>-383000</v>
+        <v>188000</v>
       </c>
       <c r="S4" t="n">
-        <v>-140000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2025-2026년 대규모 적자 및 상폐 가능성 우려. 공매도 및 주가 조작 의혹 제기.</t>
+          <t>PS일렉트로닉스의 AI 데이터센터 투자 수혜 언급 및 광통신 주가 흐름과 연관성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '공매도']</t>
+          <t>['AI', '데이터센터', '광통신']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15290</v>
+        <v>15370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.13%</t>
+          <t>'+8.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="H5" t="n">
         <v>1.95</v>
@@ -877,7 +877,7 @@
         <v>14420</v>
       </c>
       <c r="L5" t="n">
-        <v>15400</v>
+        <v>15460</v>
       </c>
       <c r="M5" t="n">
         <v>14300</v>
@@ -886,7 +886,7 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>201641769925</v>
+        <v>225425457715</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 증시 통신장비 및 부품주 강세. 14000원 지지선 확보 및 상승 기대감.</t>
+          <t>미국 통신장비 및 부품주 급등에 따른 대한광통신 상승 기대감. 120일선 저항 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['통신장비', '부품', '상승']</t>
+          <t>['통신장비', '부품주', '120일선']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5410</v>
+        <v>3755</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.44%</t>
+          <t>'+6.83%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.39</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>146</v>
+        <v>253</v>
       </c>
       <c r="H6" t="n">
-        <v>1.29</v>
+        <v>3.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5230</v>
+        <v>3515</v>
       </c>
       <c r="K6" t="n">
-        <v>5750</v>
+        <v>4120</v>
       </c>
       <c r="L6" t="n">
-        <v>5880</v>
+        <v>4140</v>
       </c>
       <c r="M6" t="n">
-        <v>5200</v>
+        <v>3730</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>46095909470</v>
+        <v>11191588491</v>
       </c>
       <c r="P6" t="n">
-        <v>8980</v>
+        <v>16110</v>
       </c>
       <c r="Q6" t="n">
-        <v>2795</v>
+        <v>2300</v>
       </c>
       <c r="R6" t="n">
-        <v>259000</v>
+        <v>-383000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-140000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>트럼프 양자암호 PQC 행정명령 및 미국 사이버보안주 폭등 수혜 기대. 삼성과 대규모 계약 체결.</t>
+          <t>25-26년 대규모 적자 예상에 따른 상폐 우려. 임상 성공 기대감과 주가 부양 시도 속 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자암호', '사이버보안', '계약']</t>
+          <t>['적자', '상폐', '임상']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3435</v>
+        <v>5440</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.34</v>
+        <v>-1.39</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3360</v>
+        <v>5230</v>
       </c>
       <c r="K7" t="n">
-        <v>3570</v>
+        <v>5750</v>
       </c>
       <c r="L7" t="n">
-        <v>3910</v>
+        <v>5880</v>
       </c>
       <c r="M7" t="n">
-        <v>3345</v>
+        <v>5200</v>
       </c>
       <c r="N7" t="n">
-        <v>1.34</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>77509509801</v>
+        <v>49033791870</v>
       </c>
       <c r="P7" t="n">
-        <v>5100</v>
+        <v>8980</v>
       </c>
       <c r="Q7" t="n">
-        <v>966</v>
+        <v>2795</v>
       </c>
       <c r="R7" t="n">
-        <v>113000</v>
+        <v>259000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>양자내성암호 행정명령 수혜 기대. 글로벌 기업 양자암호 해독키 독점 공급 전망.</t>
+          <t>트럼프 양자암호 PQC 행정명령 및 미국 보안주 상승에 따른 기대감. 삼성과의 계약 호재 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '공급']</t>
+          <t>['양자암호', 'PQC', '삼성계약']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1713000</v>
+        <v>3470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.36%</t>
+          <t>'+3.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>477</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>2329</v>
+        <v>145</v>
       </c>
       <c r="H8" t="n">
-        <v>50.2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1690000</v>
+        <v>3360</v>
       </c>
       <c r="K8" t="n">
-        <v>1686000</v>
+        <v>3570</v>
       </c>
       <c r="L8" t="n">
-        <v>1731000</v>
+        <v>3910</v>
       </c>
       <c r="M8" t="n">
-        <v>1686000</v>
+        <v>3345</v>
       </c>
       <c r="N8" t="n">
-        <v>50.27</v>
+        <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>1325856738500</v>
+        <v>79540340173</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>5100</v>
       </c>
       <c r="Q8" t="n">
-        <v>331500</v>
+        <v>966</v>
       </c>
       <c r="R8" t="n">
-        <v>18000</v>
+        <v>113000</v>
       </c>
       <c r="S8" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 선물 급등 및 인텔 사장 발언 인용. 조정 끝났다는 기대감.</t>
+          <t>트럼프 행정명령 기반 양자내성암호 글로벌 기업 독점 공급 및 미국 광통신 보안주 상승세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '급등']</t>
+          <t>['양자내성암호', '보안주', '미국']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>249500</v>
+        <v>1714000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+1.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="G9" t="n">
-        <v>2357</v>
+        <v>2308</v>
       </c>
       <c r="H9" t="n">
-        <v>46.56</v>
+        <v>50.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>248500</v>
+        <v>1690000</v>
       </c>
       <c r="K9" t="n">
-        <v>248000</v>
+        <v>1686000</v>
       </c>
       <c r="L9" t="n">
-        <v>251500</v>
+        <v>1731000</v>
       </c>
       <c r="M9" t="n">
-        <v>247500</v>
+        <v>1686000</v>
       </c>
       <c r="N9" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="O9" t="n">
-        <v>715501949500</v>
+        <v>1407853728500</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>76700</v>
+        <v>331500</v>
       </c>
       <c r="R9" t="n">
-        <v>-496000</v>
+        <v>18000</v>
       </c>
       <c r="S9" t="n">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>금리 인상 및 정치적 이슈 언급. 반도체 업황 기대감도 일부 존재.</t>
+          <t>미국 증시 반도체 선물 급등 및 인텔 사장 발언 인용. 조정 끝났다는 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['금리', '반도체', '정치']</t>
+          <t>['반도체', '선물', '급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10670</v>
+        <v>250250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.09%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>781</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>452</v>
       </c>
       <c r="G10" t="n">
-        <v>96</v>
+        <v>2389</v>
       </c>
       <c r="H10" t="n">
-        <v>19.22</v>
+        <v>46.56</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10660</v>
+        <v>248500</v>
       </c>
       <c r="K10" t="n">
-        <v>10500</v>
+        <v>248000</v>
       </c>
       <c r="L10" t="n">
-        <v>10900</v>
+        <v>251500</v>
       </c>
       <c r="M10" t="n">
-        <v>10060</v>
+        <v>247500</v>
       </c>
       <c r="N10" t="n">
-        <v>17.93</v>
+        <v>46.57</v>
       </c>
       <c r="O10" t="n">
-        <v>75885279320</v>
+        <v>799368687500</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>1760</v>
+        <v>76700</v>
       </c>
       <c r="R10" t="n">
-        <v>-437000</v>
+        <v>-496000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>거래량 증가 시 20% 상승 기대. 광통신 관련주로 분류되나 주의 종목 지정.</t>
+          <t>금리 인상 및 정치적 이슈 언급. 반도체 업황 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['거래량', '상승', '주의']</t>
+          <t>['금리', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17300</v>
+        <v>10730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'+0.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>1.29</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>198</v>
+        <v>97</v>
       </c>
       <c r="H11" t="n">
-        <v>0.45</v>
+        <v>19.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17550</v>
+        <v>10660</v>
       </c>
       <c r="K11" t="n">
-        <v>17150</v>
+        <v>10500</v>
       </c>
       <c r="L11" t="n">
-        <v>18860</v>
+        <v>10900</v>
       </c>
       <c r="M11" t="n">
-        <v>17020</v>
+        <v>10060</v>
       </c>
       <c r="N11" t="n">
-        <v>0.35</v>
+        <v>17.93</v>
       </c>
       <c r="O11" t="n">
-        <v>133340128315</v>
+        <v>80357732230</v>
       </c>
       <c r="P11" t="n">
-        <v>30550</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>6100</v>
+        <v>1760</v>
       </c>
       <c r="R11" t="n">
-        <v>65000</v>
+        <v>-437000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 보안주 상승 마감. 상용화 및 매출 발생 기업. 개미 털기 위한 인위적 주가 하락 가능성 언급.</t>
+          <t>거래량 증가 시 20% 상승 가능성 언급. 외국인 매매 동향 및 통신주 전반적 흐름과 비교.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안', '상용화', '매출']</t>
+          <t>['거래량', '통신주', '외국인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8440</v>
+        <v>17410</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-0.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="H12" t="n">
-        <v>26.66</v>
+        <v>0.45</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8610</v>
+        <v>17550</v>
       </c>
       <c r="K12" t="n">
-        <v>8600</v>
+        <v>17150</v>
       </c>
       <c r="L12" t="n">
-        <v>8610</v>
+        <v>18860</v>
       </c>
       <c r="M12" t="n">
-        <v>8430</v>
+        <v>17020</v>
       </c>
       <c r="N12" t="n">
-        <v>27.16</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
-        <v>6998518550</v>
+        <v>136027330955</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>30550</v>
       </c>
       <c r="Q12" t="n">
-        <v>8120</v>
+        <v>6100</v>
       </c>
       <c r="R12" t="n">
-        <v>-292000</v>
+        <v>65000</v>
       </c>
       <c r="S12" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>빚 과다 및 실적 부진 언급. 외인 매도세 포착. 3분기 일시적 하락 원인 분석.</t>
+          <t>미국 보안주 상승세와 연계된 엑스게이트의 2만원 돌파 기대감. 개미 털기 의혹 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['빚', '실적', '외인']</t>
+          <t>['보안주', '2만원돌파', '개미털기']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14660</v>
+        <v>8480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>394</v>
+        <v>229</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14980</v>
+        <v>8610</v>
       </c>
       <c r="K13" t="n">
-        <v>15300</v>
+        <v>8600</v>
       </c>
       <c r="L13" t="n">
-        <v>15580</v>
+        <v>8610</v>
       </c>
       <c r="M13" t="n">
-        <v>14600</v>
+        <v>8430</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O13" t="n">
-        <v>19022109685</v>
+        <v>7297679735</v>
       </c>
       <c r="P13" t="n">
-        <v>36200</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>8920</v>
+        <v>8120</v>
       </c>
       <c r="R13" t="n">
-        <v>-19000</v>
+        <v>-292000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국제 유가 상승 기대감과 에너지주 폭등 가능성 언급. 다만, 비축유 및 유가 하락 추세에 대한 우려와 테마 소멸 가능성 제기.</t>
+          <t>FLiPP 양산 시작 시 시총 급등 기대와 달리 PBR 0.6배, 외인 매도세 및 높은 부채에 대한 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국제유가', '에너지주', '테마']</t>
+          <t>['PBR', '외인매도', '부채']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84300</v>
+        <v>84700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.20%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="H14" t="n">
         <v>23.37</v>
@@ -1708,13 +1708,13 @@
         <v>86300</v>
       </c>
       <c r="M14" t="n">
-        <v>84200</v>
+        <v>83900</v>
       </c>
       <c r="N14" t="n">
         <v>23.45</v>
       </c>
       <c r="O14" t="n">
-        <v>54354833250</v>
+        <v>63931220400</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 언급 및 공매도 세력에 대한 비판. 단기 상승 기대.</t>
+          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감 및 공매도 세력과의 갈등 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
+          <t>['웨스팅하우스', '지분인수', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18530</v>
+        <v>14630</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.14%</t>
+          <t>'-2.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>157</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>221</v>
+        <v>401</v>
       </c>
       <c r="H15" t="n">
-        <v>10.64</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19130</v>
+        <v>14980</v>
       </c>
       <c r="K15" t="n">
-        <v>19160</v>
+        <v>15300</v>
       </c>
       <c r="L15" t="n">
-        <v>19340</v>
+        <v>15580</v>
       </c>
       <c r="M15" t="n">
-        <v>18500</v>
+        <v>14580</v>
       </c>
       <c r="N15" t="n">
-        <v>10.53</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>25443876110</v>
+        <v>19707866800</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>36200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>8920</v>
       </c>
       <c r="R15" t="n">
-        <v>-112000</v>
+        <v>-19000</v>
       </c>
       <c r="S15" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려. 2~3일 만원 이상 상승 가능성 언급.</t>
+          <t>국제 유가 상승 기대감과 에너지주 폭등 가능성 언급. 다만, 비축유 및 유가 하락 추세에 대한 우려와 테마 소멸 가능성 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차해지', '상승', '운동']</t>
+          <t>['국제유가', '에너지주', '테마']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31100</v>
+        <v>18650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.34</v>
+        <v>0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>786</v>
+        <v>244</v>
       </c>
       <c r="H16" t="n">
-        <v>17.16</v>
+        <v>10.64</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>32450</v>
+        <v>19130</v>
       </c>
       <c r="K16" t="n">
-        <v>32850</v>
+        <v>19160</v>
       </c>
       <c r="L16" t="n">
-        <v>32850</v>
+        <v>19340</v>
       </c>
       <c r="M16" t="n">
-        <v>30900</v>
+        <v>18500</v>
       </c>
       <c r="N16" t="n">
-        <v>17.5</v>
+        <v>10.53</v>
       </c>
       <c r="O16" t="n">
-        <v>5357146650</v>
+        <v>26764422350</v>
       </c>
       <c r="P16" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-26000</v>
+        <v>-112000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>HLB 주가 하락 베팅 유지 및 유럽 담관암 신약 신청 관련 불확실성 제기. FDA 승인 실패 시 주가 급락 가능성 언급.</t>
+          <t>대차해지 운동 참여 독려 및 2~3일 내 만원 이상 상승 가능성 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['간암', '담관암', 'FDA']</t>
+          <t>['대차해지', '운동', '주주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5890</v>
+        <v>31250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.66%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.04</v>
+        <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="G17" t="n">
-        <v>139</v>
+        <v>813</v>
       </c>
       <c r="H17" t="n">
-        <v>0.98</v>
+        <v>17.16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6310</v>
+        <v>32450</v>
       </c>
       <c r="K17" t="n">
-        <v>6390</v>
+        <v>32850</v>
       </c>
       <c r="L17" t="n">
-        <v>6450</v>
+        <v>32850</v>
       </c>
       <c r="M17" t="n">
-        <v>5630</v>
+        <v>30900</v>
       </c>
       <c r="N17" t="n">
-        <v>3.02</v>
+        <v>17.5</v>
       </c>
       <c r="O17" t="n">
-        <v>35865070275</v>
+        <v>5497405000</v>
       </c>
       <c r="P17" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>247000</v>
+        <v>-26000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>클래리티법 부결 소식과 양자내성암호 OTP 공급 계약 뉴스에 대한 엇갈린 반응. 외국인 매수세와 공매도 현황, 보안주 테마 상승세에 대한 언급.</t>
+          <t>HLB 주가 하락 베팅 유지 및 유럽 담관암 신약 신청 관련 불확실성 제기. FDA 승인 실패 시 주가 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자내성암호', 'OTP', '공매도']</t>
+          <t>['간암', '담관암', 'FDA']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2027,6 +2027,98 @@
         </is>
       </c>
       <c r="Z17" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5880</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-6.81%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E18" t="n">
+        <v>76</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45</v>
+      </c>
+      <c r="G18" t="n">
+        <v>136</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5630</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O18" t="n">
+        <v>36945895355</v>
+      </c>
+      <c r="P18" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R18" t="n">
+        <v>247000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>클래리티법 부결 소식과 삼성 공급 계약 체결 관련 혼조세. 공매도 비중이 높고 단기 급등락 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['공매도', '공급계약', '클래리티법']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>158430</t>
         </is>

--- a/data/trending_integrated_20260916_10.xlsx
+++ b/data/trending_integrated_20260916_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>798</v>
+        <v>816</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7063044930</v>
+        <v>7082613570</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13850</v>
+        <v>13760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.44%</t>
+          <t>'+28.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="n">
         <v>44</v>
       </c>
-      <c r="F3" t="n">
-        <v>42</v>
-      </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -693,7 +693,7 @@
         <v>10800</v>
       </c>
       <c r="L3" t="n">
-        <v>13900</v>
+        <v>13910</v>
       </c>
       <c r="M3" t="n">
         <v>10740</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>135962495305</v>
+        <v>150230954665</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신, 6G, 5G 대장주로서의 기대감과 함께 빛과전자와의 동반 상승 가능성 언급.</t>
+          <t>6G 통신 대장주로서의 기대감. 광통신, 5G 테마 연계 및 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '6G', '5G']</t>
+          <t>['6G', '광통신', '대장주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4680</v>
+        <v>4607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.59%</t>
+          <t>'+11.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H4" t="n">
         <v>0.74</v>
@@ -794,7 +794,7 @@
         <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>229728012497</v>
+        <v>250068035208</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스의 AI 데이터센터 투자 수혜 언급 및 광통신 주가 흐름과 연관성.</t>
+          <t>광케이블 관련 미장 상승 영향 기대. 4천원 지지선 언급 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '데이터센터', '광통신']</t>
+          <t>['광케이블', '지지선', '상한가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15370</v>
+        <v>15540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.70%</t>
+          <t>'+9.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>463</v>
+        <v>535</v>
       </c>
       <c r="H5" t="n">
         <v>1.95</v>
@@ -877,7 +877,7 @@
         <v>14420</v>
       </c>
       <c r="L5" t="n">
-        <v>15460</v>
+        <v>15700</v>
       </c>
       <c r="M5" t="n">
         <v>14300</v>
@@ -886,7 +886,7 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>225425457715</v>
+        <v>266887085110</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 통신장비 및 부품주 급등에 따른 대한광통신 상승 기대감. 120일선 저항 언급.</t>
+          <t>14000원 지지선 확보 및 상승세. 통신장비 부품 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['통신장비', '부품주', '120일선']</t>
+          <t>['지지선', '통신장비', '부품']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3755</v>
+        <v>7540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.83%</t>
+          <t>'+9.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>253</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
-        <v>3.11</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3515</v>
+        <v>6900</v>
       </c>
       <c r="K6" t="n">
-        <v>4120</v>
+        <v>6770</v>
       </c>
       <c r="L6" t="n">
-        <v>4140</v>
+        <v>8590</v>
       </c>
       <c r="M6" t="n">
-        <v>3730</v>
+        <v>6660</v>
       </c>
       <c r="N6" t="n">
-        <v>3.16</v>
+        <v>0.7</v>
       </c>
       <c r="O6" t="n">
-        <v>11191588491</v>
+        <v>65380875830</v>
       </c>
       <c r="P6" t="n">
-        <v>16110</v>
+        <v>10360</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>2965</v>
       </c>
       <c r="R6" t="n">
-        <v>-383000</v>
+        <v>75000</v>
       </c>
       <c r="S6" t="n">
-        <v>-140000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>25-26년 대규모 적자 예상에 따른 상폐 우려. 임상 성공 기대감과 주가 부양 시도 속 부정적 전망 제기.</t>
+          <t>AI 보안 대장주로서의 입지 강화. 샌즈랩의 AI 에이전트 해킹 관련 이슈 발생.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '임상']</t>
+          <t>['AI 보안', '대장주', '해킹']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5440</v>
+        <v>3755</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+6.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.39</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>161</v>
+        <v>282</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29</v>
+        <v>3.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5230</v>
+        <v>3515</v>
       </c>
       <c r="K7" t="n">
-        <v>5750</v>
+        <v>4120</v>
       </c>
       <c r="L7" t="n">
-        <v>5880</v>
+        <v>4140</v>
       </c>
       <c r="M7" t="n">
-        <v>5200</v>
+        <v>3730</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>3.16</v>
       </c>
       <c r="O7" t="n">
-        <v>49033791870</v>
+        <v>11519310590</v>
       </c>
       <c r="P7" t="n">
-        <v>8980</v>
+        <v>16110</v>
       </c>
       <c r="Q7" t="n">
-        <v>2795</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>259000</v>
+        <v>-383000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-140000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>트럼프 양자암호 PQC 행정명령 및 미국 보안주 상승에 따른 기대감. 삼성과의 계약 호재 언급.</t>
+          <t>25년, 26년 대규모 적자 공시로 인한 상폐 우려가 제기되며 급락세. 일부 투자자들은 주포의 개입 및 매도를 주장하며 탈출을 권고하고 있으나, 상한가 가능성을 언급하는 의견도 소수 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자암호', 'PQC', '삼성계약']</t>
+          <t>['적자', '상폐', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3470</v>
+        <v>5350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.27%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.34</v>
+        <v>-1.39</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3360</v>
+        <v>5230</v>
       </c>
       <c r="K8" t="n">
-        <v>3570</v>
+        <v>5750</v>
       </c>
       <c r="L8" t="n">
-        <v>3910</v>
+        <v>5880</v>
       </c>
       <c r="M8" t="n">
-        <v>3345</v>
+        <v>5200</v>
       </c>
       <c r="N8" t="n">
-        <v>1.34</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
-        <v>79540340173</v>
+        <v>50323429695</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>8980</v>
       </c>
       <c r="Q8" t="n">
-        <v>966</v>
+        <v>2795</v>
       </c>
       <c r="R8" t="n">
-        <v>113000</v>
+        <v>259000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>트럼프 행정명령 기반 양자내성암호 글로벌 기업 독점 공급 및 미국 광통신 보안주 상승세.</t>
+          <t>삼성과의 대규모 계약(4381억) 기반 급등 호재. 사이버보안 및 양자보안 관련주.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자내성암호', '보안주', '미국']</t>
+          <t>['삼성 계약', '사이버보안', '양자보안']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1714000</v>
+        <v>3420</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.42%</t>
+          <t>'+1.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>472</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>2308</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>50.2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1690000</v>
+        <v>3360</v>
       </c>
       <c r="K9" t="n">
-        <v>1686000</v>
+        <v>3570</v>
       </c>
       <c r="L9" t="n">
-        <v>1731000</v>
+        <v>3910</v>
       </c>
       <c r="M9" t="n">
-        <v>1686000</v>
+        <v>3345</v>
       </c>
       <c r="N9" t="n">
-        <v>50.27</v>
+        <v>1.34</v>
       </c>
       <c r="O9" t="n">
-        <v>1407853728500</v>
+        <v>80520210058</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>5100</v>
       </c>
       <c r="Q9" t="n">
-        <v>331500</v>
+        <v>966</v>
       </c>
       <c r="R9" t="n">
-        <v>18000</v>
+        <v>113000</v>
       </c>
       <c r="S9" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 선물 급등 및 인텔 사장 발언 인용. 조정 끝났다는 기대감.</t>
+          <t>양자내성암호 행정명령 수혜 기대. 글로벌 기업 독점 공급 사실 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '급등']</t>
+          <t>['양자보안', '독점공급', '행정명령']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250250</v>
+        <v>1714000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+1.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>781</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="G10" t="n">
-        <v>2389</v>
+        <v>2297</v>
       </c>
       <c r="H10" t="n">
-        <v>46.56</v>
+        <v>50.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>248500</v>
+        <v>1690000</v>
       </c>
       <c r="K10" t="n">
-        <v>248000</v>
+        <v>1686000</v>
       </c>
       <c r="L10" t="n">
-        <v>251500</v>
+        <v>1731000</v>
       </c>
       <c r="M10" t="n">
-        <v>247500</v>
+        <v>1686000</v>
       </c>
       <c r="N10" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="O10" t="n">
-        <v>799368687500</v>
+        <v>1492101159000</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>76700</v>
+        <v>331500</v>
       </c>
       <c r="R10" t="n">
-        <v>-496000</v>
+        <v>18000</v>
       </c>
       <c r="S10" t="n">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>금리 인상 및 정치적 이슈 언급. 반도체 업황 기대감도 일부 존재.</t>
+          <t>미국 증시 반도체 선물 급등 및 인텔 사장 발언 인용. 조정 끝났다는 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['금리', '반도체', '정치']</t>
+          <t>['반도체', '선물', '급등']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10730</v>
+        <v>249750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.66%</t>
+          <t>'+0.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>461</v>
       </c>
       <c r="G11" t="n">
-        <v>97</v>
+        <v>2450</v>
       </c>
       <c r="H11" t="n">
-        <v>19.22</v>
+        <v>46.56</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10660</v>
+        <v>248500</v>
       </c>
       <c r="K11" t="n">
-        <v>10500</v>
+        <v>248000</v>
       </c>
       <c r="L11" t="n">
-        <v>10900</v>
+        <v>251500</v>
       </c>
       <c r="M11" t="n">
-        <v>10060</v>
+        <v>247500</v>
       </c>
       <c r="N11" t="n">
-        <v>17.93</v>
+        <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>80357732230</v>
+        <v>851954980500</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1760</v>
+        <v>76700</v>
       </c>
       <c r="R11" t="n">
-        <v>-437000</v>
+        <v>-496000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가 시 20% 상승 가능성 언급. 외국인 매매 동향 및 통신주 전반적 흐름과 비교.</t>
+          <t>금리 인상 및 정치적 이슈 언급. 반도체 업황 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '통신주', '외국인']</t>
+          <t>['금리', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17410</v>
+        <v>10630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.80%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>1.29</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="H12" t="n">
-        <v>0.45</v>
+        <v>19.22</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17550</v>
+        <v>10660</v>
       </c>
       <c r="K12" t="n">
-        <v>17150</v>
+        <v>10500</v>
       </c>
       <c r="L12" t="n">
-        <v>18860</v>
+        <v>10900</v>
       </c>
       <c r="M12" t="n">
-        <v>17020</v>
+        <v>10060</v>
       </c>
       <c r="N12" t="n">
-        <v>0.35</v>
+        <v>17.93</v>
       </c>
       <c r="O12" t="n">
-        <v>136027330955</v>
+        <v>86253376110</v>
       </c>
       <c r="P12" t="n">
-        <v>30550</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>6100</v>
+        <v>1760</v>
       </c>
       <c r="R12" t="n">
-        <v>65000</v>
+        <v>-437000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 보안주 상승세와 연계된 엑스게이트의 2만원 돌파 기대감. 개미 털기 의혹 제기.</t>
+          <t>거래량 동반 시 20% 상승 가능성 언급. 외국인(JP모건) 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안주', '2만원돌파', '개미털기']</t>
+          <t>['거래량', '외국인', '조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,86 +1568,86 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8480</v>
+        <v>17310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.37%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="H13" t="n">
-        <v>26.66</v>
+        <v>0.45</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8610</v>
+        <v>17550</v>
       </c>
       <c r="K13" t="n">
-        <v>8600</v>
+        <v>17150</v>
       </c>
       <c r="L13" t="n">
-        <v>8610</v>
+        <v>18860</v>
       </c>
       <c r="M13" t="n">
-        <v>8430</v>
+        <v>17020</v>
       </c>
       <c r="N13" t="n">
-        <v>27.16</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>7297679735</v>
+        <v>139670141970</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>30550</v>
       </c>
       <c r="Q13" t="n">
-        <v>8120</v>
+        <v>6100</v>
       </c>
       <c r="R13" t="n">
-        <v>-292000</v>
+        <v>65000</v>
       </c>
       <c r="S13" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>FLiPP 양산 시작 시 시총 급등 기대와 달리 PBR 0.6배, 외인 매도세 및 높은 부채에 대한 우려.</t>
+          <t>미국 보안주 동반 상승 영향. 상용화 및 매출 발생 기반 2만원 트라이 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['PBR', '외인매도', '부채']</t>
+          <t>['미국 보안주', '상용화', '매출']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84700</v>
+        <v>14710</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G14" t="n">
-        <v>511</v>
+        <v>417</v>
       </c>
       <c r="H14" t="n">
-        <v>23.37</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>86200</v>
+        <v>14980</v>
       </c>
       <c r="K14" t="n">
-        <v>86200</v>
+        <v>15300</v>
       </c>
       <c r="L14" t="n">
-        <v>86300</v>
+        <v>15580</v>
       </c>
       <c r="M14" t="n">
-        <v>83900</v>
+        <v>14580</v>
       </c>
       <c r="N14" t="n">
-        <v>23.45</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>63931220400</v>
+        <v>20128473870</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>-105000</v>
+        <v>-19000</v>
       </c>
       <c r="S14" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감 및 공매도 세력과의 갈등 언급.</t>
+          <t>국제유가 상승 및 사우디 관련 이슈로 인한 에너지주 강세 기대감이 있으나, 비축유 방출 및 유가 하락 추세에 대한 우려도 제기. 일부 투자자들은 추가 상승을 기대하며 매수를 이어가고 있으나, 급락 가능성도 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '공매도']</t>
+          <t>['국제유가', '사우디', '에너지주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14630</v>
+        <v>84500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.34%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G15" t="n">
-        <v>401</v>
+        <v>530</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>23.37</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14980</v>
+        <v>86200</v>
       </c>
       <c r="K15" t="n">
-        <v>15300</v>
+        <v>86200</v>
       </c>
       <c r="L15" t="n">
-        <v>15580</v>
+        <v>86300</v>
       </c>
       <c r="M15" t="n">
-        <v>14580</v>
+        <v>83900</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>23.45</v>
       </c>
       <c r="O15" t="n">
-        <v>19707866800</v>
+        <v>65945529250</v>
       </c>
       <c r="P15" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-19000</v>
+        <v>-105000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국제 유가 상승 기대감과 에너지주 폭등 가능성 언급. 다만, 비축유 및 유가 하락 추세에 대한 우려와 테마 소멸 가능성 제기.</t>
+          <t>웨스팅하우스 지분 인수 관련 뉴스 기반 상승 기대. 공매도 압박 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['국제유가', '에너지주', '테마']</t>
+          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18650</v>
+        <v>8440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.51%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.11</v>
+        <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="H16" t="n">
-        <v>10.64</v>
+        <v>26.66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19130</v>
+        <v>8610</v>
       </c>
       <c r="K16" t="n">
-        <v>19160</v>
+        <v>8600</v>
       </c>
       <c r="L16" t="n">
-        <v>19340</v>
+        <v>8610</v>
       </c>
       <c r="M16" t="n">
-        <v>18500</v>
+        <v>8430</v>
       </c>
       <c r="N16" t="n">
-        <v>10.53</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>26764422350</v>
+        <v>7668884435</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-112000</v>
+        <v>-292000</v>
       </c>
       <c r="S16" t="n">
-        <v>-2000</v>
+        <v>-4000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 2~3일 내 만원 이상 상승 가능성 기대.</t>
+          <t>FLiPP 양산 시작 시 시총 급등 기대와 달리 PBR 0.6배, 외인 매도세 및 높은 부채에 대한 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '운동', '주주']</t>
+          <t>['PBR', '외인매도', '부채']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31250</v>
+        <v>18550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.34</v>
+        <v>0.11</v>
       </c>
       <c r="E17" t="n">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>813</v>
+        <v>259</v>
       </c>
       <c r="H17" t="n">
-        <v>17.16</v>
+        <v>10.64</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>32450</v>
+        <v>19130</v>
       </c>
       <c r="K17" t="n">
-        <v>32850</v>
+        <v>19160</v>
       </c>
       <c r="L17" t="n">
-        <v>32850</v>
+        <v>19340</v>
       </c>
       <c r="M17" t="n">
-        <v>30900</v>
+        <v>18500</v>
       </c>
       <c r="N17" t="n">
-        <v>17.5</v>
+        <v>10.53</v>
       </c>
       <c r="O17" t="n">
-        <v>5497405000</v>
+        <v>28090689505</v>
       </c>
       <c r="P17" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-26000</v>
+        <v>-112000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>HLB 주가 하락 베팅 유지 및 유럽 담관암 신약 신청 관련 불확실성 제기. FDA 승인 실패 시 주가 급락 가능성 언급.</t>
+          <t>대차해지 운동 동참 호소. 공매도 종식 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['간암', '담관암', 'FDA']</t>
+          <t>['대차해지', '공매도', '주가 상승']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5880</v>
+        <v>31150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-4.01%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-2.04</v>
+        <v>-0.34</v>
       </c>
       <c r="E18" t="n">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="G18" t="n">
-        <v>136</v>
+        <v>840</v>
       </c>
       <c r="H18" t="n">
-        <v>0.98</v>
+        <v>17.16</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6310</v>
+        <v>32450</v>
       </c>
       <c r="K18" t="n">
-        <v>6390</v>
+        <v>32850</v>
       </c>
       <c r="L18" t="n">
-        <v>6450</v>
+        <v>32850</v>
       </c>
       <c r="M18" t="n">
-        <v>5630</v>
+        <v>30900</v>
       </c>
       <c r="N18" t="n">
-        <v>3.02</v>
+        <v>17.5</v>
       </c>
       <c r="O18" t="n">
-        <v>36945895355</v>
+        <v>5771490675</v>
       </c>
       <c r="P18" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R18" t="n">
-        <v>247000</v>
+        <v>-26000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>클래리티법 부결 소식과 삼성 공급 계약 체결 관련 혼조세. 공매도 비중이 높고 단기 급등락 가능성 언급.</t>
+          <t>담관암 신약 관련 유럽 신청 및 FDA 승인 여부에 대한 논란이 지속. 과거 신약 실패 이력이 언급되며 투자자들의 신중론이 제기되는 가운데, 일부에서는 유럽 신청이 FDA 승인에 대한 자신감 표현으로 해석. 기관 및 외국인 매도 가능성도 거론.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '공급계약', '클래리티법']</t>
+          <t>['담관암', 'FDA', 'EMA']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2119,6 +2119,98 @@
         </is>
       </c>
       <c r="Z18" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5880</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-6.81%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E19" t="n">
+        <v>78</v>
+      </c>
+      <c r="F19" t="n">
+        <v>46</v>
+      </c>
+      <c r="G19" t="n">
+        <v>137</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5630</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O19" t="n">
+        <v>37468205255</v>
+      </c>
+      <c r="P19" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R19" t="n">
+        <v>247000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>미 클래리티법 부결, 삼성 공급 계약, 양자보안 샌즈랩 급등과 함께 주가 상승 기대감이 형성되었으나, 공매도 증가와 일부 투자자들의 매도 의견도 존재. 외국인 매수세가 유입되고 있으나 변동성 또한 큰 상황.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['클래리티법', '삼성', '양자보안']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>158430</t>
         </is>

--- a/data/trending_integrated_20260916_10.xlsx
+++ b/data/trending_integrated_20260916_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7082613570</v>
+        <v>7104812610</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오의 미투온 인수 관련, 카지노 사업 확장 기대감. 미버스 코인 급등 및 숏커버링 발생 가능성 언급.</t>
+          <t>카카오의 미투온 인수 가능성 및 합법 카지노 사업 확대 기대감. 미버스 코인 급등 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오', '인수', '미버스']</t>
+          <t>['카카오', '카지노', '인수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13760</v>
+        <v>13790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.60%</t>
+          <t>'+28.88%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F3" t="n">
         <v>50</v>
       </c>
-      <c r="F3" t="n">
-        <v>44</v>
-      </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>150230954665</v>
+        <v>155092357590</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6G 통신 대장주로서의 기대감. 광통신, 5G 테마 연계 및 급등 가능성 언급.</t>
+          <t>6G 통신 대장주로서의 기대감, 광통신, 방산 등 연관 섹터 동반 상승. 강력한 상승 움직임 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -762,13 +762,13 @@
         <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H4" t="n">
         <v>0.74</v>
@@ -794,7 +794,7 @@
         <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>250068035208</v>
+        <v>256815387385</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>광케이블 관련 미장 상승 영향 기대. 4천원 지지선 언급 및 상한가 기대.</t>
+          <t>큰 폭의 상승 및 4천원 지지선 언급, 외인 동시호가 매수 관찰. AI 데이터센터 투자 수혜 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광케이블', '지지선', '상한가']</t>
+          <t>['상승', '외인', 'AI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15540</v>
+        <v>15340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.90%</t>
+          <t>'+8.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
-        <v>535</v>
+        <v>565</v>
       </c>
       <c r="H5" t="n">
         <v>1.95</v>
@@ -886,7 +886,7 @@
         <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>266887085110</v>
+        <v>287687217385</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>14000원 지지선 확보 및 상승세. 통신장비 부품 동반 상승 기대.</t>
+          <t>14000원 지지선 확보 및 상승 출발, 통신장비/부품 섹터 동반 상승 기대. 주포의 움직임 주목.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['지지선', '통신장비', '부품']</t>
+          <t>['지지선', '통신장비', '주포']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7540</v>
+        <v>7340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.28%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
         <v>0.79</v>
@@ -978,7 +978,7 @@
         <v>0.7</v>
       </c>
       <c r="O6" t="n">
-        <v>65380875830</v>
+        <v>67494834735</v>
       </c>
       <c r="P6" t="n">
         <v>10360</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 보안 대장주로서의 입지 강화. 샌즈랩의 AI 에이전트 해킹 관련 이슈 발생.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '해킹']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3755</v>
+        <v>3710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.83%</t>
+          <t>'+5.55%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H7" t="n">
         <v>3.11</v>
@@ -1064,13 +1064,13 @@
         <v>4140</v>
       </c>
       <c r="M7" t="n">
-        <v>3730</v>
+        <v>3710</v>
       </c>
       <c r="N7" t="n">
         <v>3.16</v>
       </c>
       <c r="O7" t="n">
-        <v>11519310590</v>
+        <v>11801398877</v>
       </c>
       <c r="P7" t="n">
         <v>16110</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>25년, 26년 대규모 적자 공시로 인한 상폐 우려가 제기되며 급락세. 일부 투자자들은 주포의 개입 및 매도를 주장하며 탈출을 권고하고 있으나, 상한가 가능성을 언급하는 의견도 소수 존재.</t>
+          <t>연속적인 적자 및 재무 상태 악화에 대한 심각한 우려 표출. 상장폐지 수준의 위험 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '공매도']</t>
+          <t>['적자', '재무', '상폐']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5350</v>
+        <v>3475</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+3.42%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.39</v>
+        <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5230</v>
+        <v>3360</v>
       </c>
       <c r="K8" t="n">
-        <v>5750</v>
+        <v>3570</v>
       </c>
       <c r="L8" t="n">
-        <v>5880</v>
+        <v>3910</v>
       </c>
       <c r="M8" t="n">
-        <v>5200</v>
+        <v>3345</v>
       </c>
       <c r="N8" t="n">
-        <v>2.68</v>
+        <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>50323429695</v>
+        <v>81384879646</v>
       </c>
       <c r="P8" t="n">
-        <v>8980</v>
+        <v>5100</v>
       </c>
       <c r="Q8" t="n">
-        <v>2795</v>
+        <v>966</v>
       </c>
       <c r="R8" t="n">
-        <v>259000</v>
+        <v>113000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성과의 대규모 계약(4381억) 기반 급등 호재. 사이버보안 및 양자보안 관련주.</t>
+          <t>양자내성암호 및 양자보안 관련 글로벌 기업 언급, 한국첨단소재의 독점 공급 기대. 매집 및 이슈 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성 계약', '사이버보안', '양자보안']</t>
+          <t>['양자암호', '보안', '매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3420</v>
+        <v>190900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.79%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.34</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>75.66</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3360</v>
+        <v>187100</v>
       </c>
       <c r="K9" t="n">
-        <v>3570</v>
+        <v>187200</v>
       </c>
       <c r="L9" t="n">
-        <v>3910</v>
+        <v>195900</v>
       </c>
       <c r="M9" t="n">
-        <v>3345</v>
+        <v>186100</v>
       </c>
       <c r="N9" t="n">
-        <v>1.34</v>
+        <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>80520210058</v>
+        <v>340770429900</v>
       </c>
       <c r="P9" t="n">
-        <v>5100</v>
+        <v>243500</v>
       </c>
       <c r="Q9" t="n">
-        <v>966</v>
+        <v>61800</v>
       </c>
       <c r="R9" t="n">
-        <v>113000</v>
+        <v>22000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>양자내성암호 행정명령 수혜 기대. 글로벌 기업 독점 공급 사실 기반 상승 전망.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['양자보안', '독점공급', '행정명령']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1714000</v>
+        <v>5330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.42%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.39</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>474</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>2297</v>
+        <v>151</v>
       </c>
       <c r="H10" t="n">
-        <v>50.2</v>
+        <v>1.29</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1690000</v>
+        <v>5230</v>
       </c>
       <c r="K10" t="n">
-        <v>1686000</v>
+        <v>5750</v>
       </c>
       <c r="L10" t="n">
-        <v>1731000</v>
+        <v>5880</v>
       </c>
       <c r="M10" t="n">
-        <v>1686000</v>
+        <v>5200</v>
       </c>
       <c r="N10" t="n">
-        <v>50.27</v>
+        <v>2.68</v>
       </c>
       <c r="O10" t="n">
-        <v>1492101159000</v>
+        <v>51062610670</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>8980</v>
       </c>
       <c r="Q10" t="n">
-        <v>331500</v>
+        <v>2795</v>
       </c>
       <c r="R10" t="n">
-        <v>18000</v>
+        <v>259000</v>
       </c>
       <c r="S10" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 선물 급등 및 인텔 사장 발언 인용. 조정 끝났다는 기대감.</t>
+          <t>미국 보안주 급등, 양자보안 구축 의무화 관련 기대감. 삼성과의 계약 규모에 대한 긍정적 전망 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '급등']</t>
+          <t>['양자보안', '보안주', '계약']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>249750</v>
+        <v>1712000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.50%</t>
+          <t>'+1.30%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="G11" t="n">
-        <v>2450</v>
+        <v>2224</v>
       </c>
       <c r="H11" t="n">
-        <v>46.56</v>
+        <v>50.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248500</v>
+        <v>1690000</v>
       </c>
       <c r="K11" t="n">
-        <v>248000</v>
+        <v>1686000</v>
       </c>
       <c r="L11" t="n">
-        <v>251500</v>
+        <v>1731000</v>
       </c>
       <c r="M11" t="n">
-        <v>247500</v>
+        <v>1686000</v>
       </c>
       <c r="N11" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="O11" t="n">
-        <v>851954980500</v>
+        <v>1544731475000</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>76700</v>
+        <v>331500</v>
       </c>
       <c r="R11" t="n">
-        <v>-496000</v>
+        <v>18000</v>
       </c>
       <c r="S11" t="n">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>금리 인상 및 정치적 이슈 언급. 반도체 업황 기대감도 일부 존재.</t>
+          <t>인텔 사장 발언 인용, 반도체 수요 증가 기대. 자사주 매입 및 성과급 지급 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['금리', '반도체', '정치']</t>
+          <t>['반도체', '수요', '자사주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10630</v>
+        <v>250000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'+0.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>465</v>
       </c>
       <c r="G12" t="n">
-        <v>102</v>
+        <v>2408</v>
       </c>
       <c r="H12" t="n">
-        <v>19.22</v>
+        <v>46.56</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10660</v>
+        <v>248500</v>
       </c>
       <c r="K12" t="n">
-        <v>10500</v>
+        <v>248000</v>
       </c>
       <c r="L12" t="n">
-        <v>10900</v>
+        <v>251500</v>
       </c>
       <c r="M12" t="n">
-        <v>10060</v>
+        <v>247500</v>
       </c>
       <c r="N12" t="n">
-        <v>17.93</v>
+        <v>46.57</v>
       </c>
       <c r="O12" t="n">
-        <v>86253376110</v>
+        <v>900264692750</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1760</v>
+        <v>76700</v>
       </c>
       <c r="R12" t="n">
-        <v>-437000</v>
+        <v>-496000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 동반 시 20% 상승 가능성 언급. 외국인(JP모건) 조작 의혹 제기.</t>
+          <t>금리 인상 및 정치적 이슈에 대한 부정적 언급, 반도체 섹터 언급. 불확실성 증폭.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['거래량', '외국인', '조작']</t>
+          <t>['금리인상', '반도체', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17310</v>
+        <v>13310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.37%</t>
+          <t>'+0.08%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="H13" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17550</v>
+        <v>13300</v>
       </c>
       <c r="K13" t="n">
-        <v>17150</v>
+        <v>13490</v>
       </c>
       <c r="L13" t="n">
-        <v>18860</v>
+        <v>13940</v>
       </c>
       <c r="M13" t="n">
-        <v>17020</v>
+        <v>13230</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>139670141970</v>
+        <v>9667723835</v>
       </c>
       <c r="P13" t="n">
-        <v>30550</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>6100</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>65000</v>
+        <v>-26000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 보안주 동반 상승 영향. 상용화 및 매출 발생 기반 2만원 트라이 기대.</t>
+          <t>주가 하락 및 부진한 흐름에 대한 불만 토로, 영양가 없는 호재 언급. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['미국 보안주', '상용화', '매출']</t>
+          <t>['주가', '호재', '투자심리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14710</v>
+        <v>10610</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>417</v>
+        <v>112</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>19.22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14980</v>
+        <v>10660</v>
       </c>
       <c r="K14" t="n">
-        <v>15300</v>
+        <v>10500</v>
       </c>
       <c r="L14" t="n">
-        <v>15580</v>
+        <v>10900</v>
       </c>
       <c r="M14" t="n">
-        <v>14580</v>
+        <v>10060</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>17.93</v>
       </c>
       <c r="O14" t="n">
-        <v>20128473870</v>
+        <v>88309775025</v>
       </c>
       <c r="P14" t="n">
-        <v>36200</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>8920</v>
+        <v>1760</v>
       </c>
       <c r="R14" t="n">
-        <v>-19000</v>
+        <v>-437000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 사우디 관련 이슈로 인한 에너지주 강세 기대감이 있으나, 비축유 방출 및 유가 하락 추세에 대한 우려도 제기. 일부 투자자들은 추가 상승을 기대하며 매수를 이어가고 있으나, 급락 가능성도 언급.</t>
+          <t>의미 없는 투자 투주 언급, 거래량 증가 시 20% 상승 가능성 기대. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국제유가', '사우디', '에너지주']</t>
+          <t>['거래량', '상승', '외인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84500</v>
+        <v>8460</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.08</v>
+        <v>-0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="F15" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>530</v>
+        <v>241</v>
       </c>
       <c r="H15" t="n">
-        <v>23.37</v>
+        <v>26.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>86200</v>
+        <v>8610</v>
       </c>
       <c r="K15" t="n">
-        <v>86200</v>
+        <v>8600</v>
       </c>
       <c r="L15" t="n">
-        <v>86300</v>
+        <v>8610</v>
       </c>
       <c r="M15" t="n">
-        <v>83900</v>
+        <v>8430</v>
       </c>
       <c r="N15" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>65945529250</v>
+        <v>7954951230</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-105000</v>
+        <v>-292000</v>
       </c>
       <c r="S15" t="n">
-        <v>-21000</v>
+        <v>-4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 관련 뉴스 기반 상승 기대. 공매도 압박 언급.</t>
+          <t>삼성디스플레이와 비교하며 실적 부진 및 높은 부채 비율 우려. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
+          <t>['부채', '환율', '외인']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8440</v>
+        <v>84600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.5</v>
+        <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>236</v>
+        <v>541</v>
       </c>
       <c r="H16" t="n">
-        <v>26.66</v>
+        <v>23.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8610</v>
+        <v>86200</v>
       </c>
       <c r="K16" t="n">
-        <v>8600</v>
+        <v>86200</v>
       </c>
       <c r="L16" t="n">
-        <v>8610</v>
+        <v>86300</v>
       </c>
       <c r="M16" t="n">
-        <v>8430</v>
+        <v>83900</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>23.45</v>
       </c>
       <c r="O16" t="n">
-        <v>7668884435</v>
+        <v>67986800300</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>-292000</v>
+        <v>-105000</v>
       </c>
       <c r="S16" t="n">
-        <v>-4000</v>
+        <v>-21000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>FLiPP 양산 시작 시 시총 급등 기대와 달리 PBR 0.6배, 외인 매도세 및 높은 부채에 대한 우려.</t>
+          <t>웨스팅하우스 지분 인수 관련 뉴스 기반 상승 기대. 공매도 압박 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['PBR', '외인매도', '부채']</t>
+          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18550</v>
+        <v>14680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>163</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="G17" t="n">
-        <v>259</v>
+        <v>428</v>
       </c>
       <c r="H17" t="n">
-        <v>10.64</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19130</v>
+        <v>14980</v>
       </c>
       <c r="K17" t="n">
-        <v>19160</v>
+        <v>15300</v>
       </c>
       <c r="L17" t="n">
-        <v>19340</v>
+        <v>15580</v>
       </c>
       <c r="M17" t="n">
-        <v>18500</v>
+        <v>14580</v>
       </c>
       <c r="N17" t="n">
-        <v>10.53</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>28090689505</v>
+        <v>20351195130</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-112000</v>
+        <v>-19000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차해지 운동 동참 호소. 공매도 종식 및 주가 상승 기대.</t>
+          <t>국제유가 상승 및 사우디 관련 이슈로 인한 에너지주 강세 기대감이 있으나, 비축유 방출 및 유가 하락 추세에 대한 우려도 제기. 일부 투자자들은 추가 상승을 기대하며 매수를 이어가고 있으나, 급락 가능성도 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주가 상승']</t>
+          <t>['국제유가', '사우디', '에너지주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31150</v>
+        <v>17190</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.01%</t>
+          <t>'-2.05%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.34</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="F18" t="n">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>840</v>
+        <v>270</v>
       </c>
       <c r="H18" t="n">
-        <v>17.16</v>
+        <v>0.45</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32450</v>
+        <v>17550</v>
       </c>
       <c r="K18" t="n">
-        <v>32850</v>
+        <v>17150</v>
       </c>
       <c r="L18" t="n">
-        <v>32850</v>
+        <v>18860</v>
       </c>
       <c r="M18" t="n">
-        <v>30900</v>
+        <v>17020</v>
       </c>
       <c r="N18" t="n">
-        <v>17.5</v>
+        <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>5771490675</v>
+        <v>141255414190</v>
       </c>
       <c r="P18" t="n">
-        <v>69200</v>
+        <v>30550</v>
       </c>
       <c r="Q18" t="n">
-        <v>24150</v>
+        <v>6100</v>
       </c>
       <c r="R18" t="n">
-        <v>-26000</v>
+        <v>65000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>담관암 신약 관련 유럽 신청 및 FDA 승인 여부에 대한 논란이 지속. 과거 신약 실패 이력이 언급되며 투자자들의 신중론이 제기되는 가운데, 일부에서는 유럽 신청이 FDA 승인에 대한 자신감 표현으로 해석. 기관 및 외국인 매도 가능성도 거론.</t>
+          <t>미국 보안주 상승에도 불구하고 상대적 약세에 대한 실망감 표출. 2만원 목표 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA', 'EMA']</t>
+          <t>['보안주', '양자', '변동성']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,97 +2120,281 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5880</v>
+        <v>18530</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-3.14%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-2.04</v>
+        <v>0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>137</v>
+        <v>265</v>
       </c>
       <c r="H19" t="n">
-        <v>0.98</v>
+        <v>10.64</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6310</v>
+        <v>19130</v>
       </c>
       <c r="K19" t="n">
-        <v>6390</v>
+        <v>19160</v>
       </c>
       <c r="L19" t="n">
-        <v>6450</v>
+        <v>19340</v>
       </c>
       <c r="M19" t="n">
-        <v>5630</v>
+        <v>18500</v>
       </c>
       <c r="N19" t="n">
-        <v>3.02</v>
+        <v>10.53</v>
       </c>
       <c r="O19" t="n">
-        <v>37468205255</v>
+        <v>29140799025</v>
       </c>
       <c r="P19" t="n">
-        <v>11370</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>247000</v>
+        <v>-112000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미 클래리티법 부결, 삼성 공급 계약, 양자보안 샌즈랩 급등과 함께 주가 상승 기대감이 형성되었으나, 공매도 증가와 일부 투자자들의 매도 의견도 존재. 외국인 매수세가 유입되고 있으나 변동성 또한 큰 상황.</t>
+          <t>대차해지 운동 동참 호소. 공매도 종식 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['대차해지', '공매도', '주가 상승']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>31200</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-3.85%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E20" t="n">
+        <v>176</v>
+      </c>
+      <c r="F20" t="n">
+        <v>109</v>
+      </c>
+      <c r="G20" t="n">
+        <v>898</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>32450</v>
+      </c>
+      <c r="K20" t="n">
+        <v>32850</v>
+      </c>
+      <c r="L20" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30900</v>
+      </c>
+      <c r="N20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5910192800</v>
+      </c>
+      <c r="P20" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-26000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>간암 및 담관암 신약 승인 관련 불확실성 및 유럽 신청 시점에 대한 의구심 제기. 하방 베팅 의견.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['담관암', 'FDA', '신약']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5920</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-6.18%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G21" t="n">
+        <v>149</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5630</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O21" t="n">
+        <v>37925306740</v>
+      </c>
+      <c r="P21" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R21" t="n">
+        <v>247000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>클래리티법 부결에 따른 영향 분석 및 삼성 계약 언급. 공매도 비중 증가 및 가격 하락 우려.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
         <v>0.5</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>['클래리티법', '삼성', '양자보안']</t>
-        </is>
-      </c>
-      <c r="X19" t="n">
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['클래리티법', '공매도', '계약']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
         <v>2</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>158430</t>
         </is>
